--- a/daily_matches/job_matches_2026-07-06.xlsx
+++ b/daily_matches/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied Data Scientist, Finance AI Evaluation &amp; Datasets</t>
+          <t>Senior Software Engineer (Agentic Search) - Billing</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,17 +486,157 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, BigQuery, Kinesis, Snowflake, BigQuery, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdbc07f22f8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=69769bc525f24703</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=984c0795a9397ea4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mid-Level Data Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Everforth ECS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3dd222f519d9192</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Agentic Search) - Billing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tavily</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Kinesis, Snowflake, BigQuery, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7af6ab5b1c008e57</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=994484e343666267</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-06.xlsx
+++ b/daily_matches/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Agentic Search) - Billing</t>
+          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Kinesis, Snowflake, BigQuery, Kafka, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69769bc525f24703</t>
+          <t>https://www.indeed.com/viewjob?jk=bafdefe3d6f58e5e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984c0795a9397ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=51511a1532d9a343</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>Senior Data Engineer - Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, Glue, Redshift, Kinesis, CI/CD, Redshift, PySpark, Kafka, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3dd222f519d9192</t>
+          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Agentic Search) - Billing</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tavily</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Kinesis, Snowflake, BigQuery, Kafka, Python, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af6ab5b1c008e57</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5e85e93f663e24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior ML/AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>CareScout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,21 +622,231 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer - Remote or Hybrid Eden Prairie, MN or Schaumburg, IL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60ef76093c07a3c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paperless Parts</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1777f0045c231e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Paperless Parts</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16bcaf7696976f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vestmark</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=994484e343666267</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8df903fde2a73ac8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CareScout</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Devops Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1955afbb6022f653</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-06.xlsx
+++ b/daily_matches/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Azure ML, S3, EC2, Glue, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafdefe3d6f58e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51511a1532d9a343</t>
+          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Technology</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Kinesis, CI/CD, Redshift, PySpark, Kafka, MySQL, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bdb97431796fc6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5e85e93f663e24</t>
+          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Digital - Forward Deployed Engineer (FDE) - Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, MLflow, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7ecec511e40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=91c1cc22f7103164</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer - Remote or Hybrid Eden Prairie, MN or Schaumburg, IL</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AnswersNow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ef76093c07a3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4397539578f6cf5c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paperless Parts</t>
+          <t>Tennant Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, AWS SageMaker, Azure ML, Databricks, Kafka, Hadoop, Tableau, Power BI, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1777f0045c231e0</t>
+          <t>https://www.indeed.com/viewjob?jk=621cf7926d14d01b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paperless Parts</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16bcaf7696976f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=28d82ab162d1f1ae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vestmark</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>Data Scientist, Docker, CI/CD, Git, Databricks, PySpark, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,252 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df903fde2a73ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CareScout</t>
+          <t>Onsite Partners, Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, S3, Glue, Redshift, Git, Redshift, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4120e8feb4ee57</t>
+          <t>https://www.indeed.com/viewjob?jk=c78cff169ad66785</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer (GCP)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Onsite Partners, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Redshift, Git, Redshift, Power BI, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbd6c66aa3d11be3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Marchex</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01ad1ab2524213c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Agent Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PENCIL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Python, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88f7e88f0c90a17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer (AI-Powered)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Planet DDS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1955afbb6022f653</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=360fe49410179650</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Snowflake Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3a23d88f1b4dfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Automation &amp; Executive Operations Fellow (Remote)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Limitless Brands</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Docker, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=526dca52a6ce24cc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-06.xlsx
+++ b/daily_matches/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Artificial (AI) Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>VELOX Media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Azure ML, S3, EC2, Glue, Docker</t>
+          <t>LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb05c2c61999715</t>
+          <t>https://www.indeed.com/viewjob?jk=7122fa8be88821f7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>EnsoData</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d912db59816e5636</t>
+          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, Kubernetes</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec02878ccd2d529</t>
+          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Advanced Technology Search Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python</t>
+          <t>Data Scientist, Generative AI, TensorFlow, MLflow, CI/CD, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221db76d815c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a675a521f09d4a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Digital - Forward Deployed Engineer (FDE) - Associate</t>
+          <t>Senior Data Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Data Lake, Kubernetes, Git, Snowflake, Cassandra, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c1cc22f7103164</t>
+          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AnswersNow</t>
+          <t>Circadence Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, R</t>
+          <t>RAG, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4397539578f6cf5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2718a7cf84c3ea02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer Level 2 (FullStack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tennant Company</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Ohio City, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, AWS SageMaker, Azure ML, Databricks, Kafka, Hadoop, Tableau, Power BI, R</t>
+          <t>Data Scientist, Generative AI, CI/CD, Terraform, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621cf7926d14d01b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d23c04648738f97</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Jenkins, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d82ab162d1f1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>ClubReady</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, CI/CD, Git, Databricks, PySpark, NoSQL, Python, SQL, R</t>
+          <t>RAG, Cortex, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e821925ed2bce</t>
+          <t>https://www.indeed.com/viewjob?jk=c79a5532e656fa04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Onsite Partners, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Git, Redshift, Power BI, Quicksight, Python, SQL</t>
+          <t>AI Engineer, RAG, FastAPI, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78cff169ad66785</t>
+          <t>https://www.indeed.com/viewjob?jk=d34836f04b426b9a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Onsite Partners, Inc</t>
+          <t>Canary Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Git, Redshift, Power BI, Quicksight, Python, SQL</t>
+          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd6c66aa3d11be3</t>
+          <t>https://www.indeed.com/viewjob?jk=b4fd8be2ac2acbae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UI Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marchex</t>
+          <t>C&amp;W Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ad1ab2524213c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec1a91015c43fafc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agent Architect</t>
+          <t>Senior Build &amp; Server Engineer - Personal Media</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PENCIL</t>
+          <t>Plex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Python, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88f7e88f0c90a17</t>
+          <t>https://www.indeed.com/viewjob?jk=af517bda843eacca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer (AI-Powered)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Recorded Future</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Cortex, CI/CD, Snowflake, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360fe49410179650</t>
+          <t>https://www.indeed.com/viewjob?jk=384f0f2bca3d62da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>AI &amp; Data Science Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlisle, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, LLaMA, TensorFlow, PyTorch, OpenCV, FastAPI, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3a23d88f1b4dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e98f708b5e6218bb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Automation &amp; Executive Operations Fellow (Remote)</t>
+          <t>Senior Data Analyst - Gaming Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Limitless Brands</t>
+          <t>Accel Entertainment Gaming, LLC.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burr Ridge, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,77 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526dca52a6ce24cc</t>
+          <t>https://www.indeed.com/viewjob?jk=50f95edc7b2c9318</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1e16808db99b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Circadence Corporation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709127f9c7760d50</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-06.xlsx
+++ b/daily_matches/job_matches_2026-07-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial (AI) Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VELOX Media</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, Git, MySQL</t>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, AWS SageMaker, Docker, Kubernetes, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7122fa8be88821f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2f054db5cf496e23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior AI Data Scientist I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EnsoData</t>
+          <t>Exelixis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, S3, Glue, CI/CD, Git, Databricks, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c200b9c6c495978</t>
+          <t>https://www.indeed.com/viewjob?jk=a3699932d60be278</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Software Developer, Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, PostgreSQL, MySQL, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e687931092830755</t>
+          <t>https://www.indeed.com/viewjob?jk=cf35f133cdd540ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Analytics Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Advanced Technology Search Group</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, MLflow, CI/CD, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a675a521f09d4a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d98ab236da7f358</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (FedRAMP)</t>
+          <t>Senior Engineer, DevOps (US)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Code and Theory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Kubernetes, Git, Snowflake, Cassandra, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f839f1132ce8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7c44a7ae12f1264e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Engineer (Azure, Terraform, Kubernetes)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Circadence Corporation</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2718a7cf84c3ea02</t>
+          <t>https://www.indeed.com/viewjob?jk=adfc859f88eb2915</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Level 2 (FullStack)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Recolabs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ohio City, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, CI/CD, Terraform, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d23c04648738f97</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0bbb055a6c22c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Consultant, Data Science – Elevate – Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Simon-Kucher &amp; Partners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, XGBoost, LightGBM, CatBoost, AWS SageMaker, Git, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9cd3a78dfa855</t>
+          <t>https://www.indeed.com/viewjob?jk=761368121f8323aa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Developer/Framework Specialists</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ClubReady</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79a5532e656fa04</t>
+          <t>https://www.indeed.com/viewjob?jk=188eebe0c624a564</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34836f04b426b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=660813ceffa3da5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Senior Software Engineer – Cloud-Native Applications</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Canary Technologies</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4fd8be2ac2acbae</t>
+          <t>https://www.indeed.com/viewjob?jk=61eba61db8d1d33f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C&amp;W Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec1a91015c43fafc</t>
+          <t>https://www.indeed.com/viewjob?jk=6266f795f6f70349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Build &amp; Server Engineer - Personal Media</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Plex</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+          <t>Generative AI, Jenkins, Git, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af517bda843eacca</t>
+          <t>https://www.indeed.com/viewjob?jk=956a30d7f302213c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recorded Future</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384f0f2bca3d62da</t>
+          <t>https://www.indeed.com/viewjob?jk=63633a8200979a09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI &amp; Data Science Intern</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>Tavant Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carlisle, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, TensorFlow, PyTorch, OpenCV, FastAPI, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98f708b5e6218bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e27ac038e5b2bb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Gaming Analytics</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>Brightspeed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Burr Ridge, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+          <t>Data Scientist, RAG, Data Lake, Power BI, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f95edc7b2c9318</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e32f7fa137ab1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Gaming Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+          <t>RAG, Docker, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1e16808db99b32</t>
+          <t>https://www.indeed.com/viewjob?jk=4d3642bb248ed5aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Circadence Corporation</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
+          <t>RAG, Gemini, PostgreSQL, Tableau, Power BI, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,77 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709127f9c7760d50</t>
+          <t>https://www.indeed.com/viewjob?jk=2739902e00a52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b23513021c85687</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Weston, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2360cb81af1e39f</t>
         </is>
       </c>
     </row>
